--- a/lores.xlsx
+++ b/lores.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daeva\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daeva\Desktop\Card_game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777874F3-EE50-47BC-9D47-8A9B982E0FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFC1C52-A0B3-417E-AD27-4B53021C0836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E9E6528D-FBE9-4018-A878-CDA73BAA7273}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E9E6528D-FBE9-4018-A878-CDA73BAA7273}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/lores.xlsx
+++ b/lores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daeva\Desktop\Card_game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBFC1C52-A0B3-417E-AD27-4B53021C0836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C5FAD4-F842-4B55-A44B-FAEDB9E5FFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E9E6528D-FBE9-4018-A878-CDA73BAA7273}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="120">
   <si>
     <t>name</t>
   </si>
@@ -322,6 +322,78 @@
   </si>
   <si>
     <t>Thirteen year old Serilla is a tragic anomaly who has known absolutely nothing of the world beyond the damp and lightless underground crypts of the human citadel. Stripped of a normal childhood, she was subjected to horrific forbidden techniques and heavily modified with unknown ancient artifacts to become the ultimate Berserker. Wielding immense raw physical strength in melee combat without the need for elemental magic, she exists solely to destroy the enemies of the church and execute secretive tasks that the holy order wishes to keep permanently buried. Now deployed into the Dark Glade alongside Corvus and Aurora, Serilla operates with the cold and unfeeling efficiency of a living weapon. Her completely detached and sickly demeanor leaves her new party members profoundly bewildered, as she expresses no fear, desire, or recognizable human emotion. To the church, she is a miraculous trump card in the war against the demon king, but to those who fight beside her, she is a haunting reminder of the darkest lengths humanity will go to ensure its own survival.</t>
+  </si>
+  <si>
+    <t>Elowen Wolfcrag</t>
+  </si>
+  <si>
+    <t>Evander Wolfcrag</t>
+  </si>
+  <si>
+    <t>Eva Hearthgale</t>
+  </si>
+  <si>
+    <t>The Cursed Child</t>
+  </si>
+  <si>
+    <t>At seventeen years old, Elowen is a quiet and incredibly kindhearted Earth Scout who faces a deeply uncertain future with a soft and enduring smile. Born into the secluded lycanthrope tribe of the dark forest, she was cursed with a highly volatile wolf transformation cycle that terrified her people, leading to a death sentence she narrowly escaped thanks to her father Evander. While she currently lacks the seasoned battle experience to be considered a renowned warrior, she uses her natural agility and raw earthen melee strikes to survive their grueling life in exile. She relies heavily on her father to guide her as she struggles to understand and control the wild power coursing through her veins. Currently her days are spent roaming the shadowy woods and escorting their human contact Eva to the eastern woodlands border for clandestine meetings with elven emissaries. Elowen understands very little about the complex politics of the growing alliance against the demon king, but she trusts her small chosen family unconditionally. Where others might sense deception in the cunning beast tamer Eva, Elowen detects absolutely zero hostility in her scent, finding the human’s presence to be a warm and uplifting comfort in an otherwise terrifying world.</t>
+  </si>
+  <si>
+    <t>The Exiled Shield</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>At sixty three years of age, Evander is a wise and surprisingly swift Tank who relies entirely on raw physical endurance and melee prowess to protect his small family. Once a highly respected shapeshifter warrior and the head bodyguard to the chief of the dark forest lycanthrope tribe, he threw his prestigious position away to rescue the cursed child Elowen from execution. Though a seasoned veteran among his own kind, he is just one capable warrior in a vast and dangerous world, holding his own against lesser demonic threats while prioritizing defense over glorious combat. His primary focus is no longer tribal politics, but rather keeping his vulnerable daughter safe at all costs as they navigate their banishment. Knowing he could not teach Elowen to master her volatile transformations alone, Evander made a desperate pact with the elven and beastfolk council of the eastern woodlands. In exchange for providing them with crucial intelligence regarding the human realm and the encroaching demonic forces, the council agreed to grant Elowen sanctuary and the specialized training she so desperately needs. Wandering the treacherous dark forest as an outcast, he remains a deeply caring father figure whose sharp tactical mind and steady blade ensure they survive long enough to see Elowen master her terrible curse.</t>
+  </si>
+  <si>
+    <t>The Gale Whisperer</t>
+  </si>
+  <si>
+    <t>Beast Tamer</t>
+  </si>
+  <si>
+    <t>Eva is an incredibly smart and upbeat twenty eight year old Air Beast Tamer whose cunning nature serves her well in the treacherous depths of the dark forest. Labeled as the Beast Master of the Gale by those few who know of her talents, she honed her connection to wildlife to a degree rarely seen even among elven druids, allowing her to converse directly with the creatures of the woods. While she is far from being a legendary champion capable of vanquishing demon lords, her unique magic allows her to safely navigate deadly territories by avoiding conflicts with magical beasts altogether. She rarely travels alone, accompanied everywhere by her imposing black direwolf companion Lycaon. During one of her many dangerous expeditions into the dark forest, Eva crossed paths with the exiled lycanthropes Evander and Elowen, a meeting that immediately captured her attention. She was entirely fascinated by Elowen, sensing a highly unique and otherworldly presence radiating from the young cursed girl. Driven by a mixture of deep curiosity and a genuine desire to help the alliance against the demon king, she allied with the outcasts to safely transfer vital knowledge from the human territory of Silver Gale directly to the elven woodlands.</t>
+  </si>
+  <si>
+    <t>Bran Bloodseeker</t>
+  </si>
+  <si>
+    <t>Marpha</t>
+  </si>
+  <si>
+    <t>Samara blackheart</t>
+  </si>
+  <si>
+    <t>The Dark Knight</t>
+  </si>
+  <si>
+    <t>Dark Paladin</t>
+  </si>
+  <si>
+    <t>Bran is a one hundred and twenty nine year old Dark Paladin whose very existence challenges the rigid traditions of the world. Born in the iron plains as a taboo half elf and half dwarf, he endured a harsh upbringing filled with intense prejudice from the dwarven clans who viewed his mixed blood as an unforgivable eyesore. Unwanted wherever he traveled, he eventually broke through the eastern borders and found much needed solace among the northern elven tribes of the woodlands. There, he was taken in and trained by the radiant Melisande Sunward, blooming into a highly promising warrior who originally possessed a pure affinity for the Light. Under Melisande's gentle guidance, Bran developed a profound and deeply mutual affection for his mentor, finding a sense of belonging he had never known. This fragile peace was violently ripped away during the second demon war when he learned that Samara Blackheart had slaughtered the woman he loved. The devastating news completely broke his mind, causing his radiant Light affinity to vanish entirely and leaving him with nothing but raw desperation and reckless abandon. Now fighting without elemental magic in brutal melee combat, the grieving paladin has sworn a blood oath to hunt down the Calamity Demon and completely eradicate her entire kin.</t>
+  </si>
+  <si>
+    <t>Goddess of the Wild</t>
+  </si>
+  <si>
+    <t>Sword Saint</t>
+  </si>
+  <si>
+    <t>Estimated to be nearly seven centuries old, Marpha is an ancient high elf and a profound mystery of the olden world. Wielding the Wild element as a peerless Sword Saint, she relies on graceful melee combat rather than distant spellcasting to fell her adversaries. She was once revered across the realms as the elven queen and the living goddess of the wild, presiding over a unified continent during a golden age of peace that lasted for over two centuries. Her tranquil reign was shattered when her beloved elven king was corrupted by an unknown dark magic, a tragic fall from grace that twisted his mind and ultimately transformed him into the world's very first demon king. Forced to make an unbearable choice to save her realm, Marpha struck down the corrupted king, ending a horrific century of darkness that had plagued the continent. However, her sacrifice did not end there. To halt the virulent corruption that first infected her king, she traveled to the perilous dark gale and embedded herself directly within the beating heart of the miasma source. For three hundred years, the ancient elven queen laid completely dormant in that twisted land, acting as a living seal against the darkness until her recent awakening.</t>
+  </si>
+  <si>
+    <t>The Calamity Demon</t>
+  </si>
+  <si>
+    <t>Soul Harvester</t>
+  </si>
+  <si>
+    <t>Melee, Magic</t>
+  </si>
+  <si>
+    <t>Known universally as the Calamity Demon, Samara Blackheart is an estimated four hundred and ten year old entity whose very existence is treated as a natural disaster. Fighting as a Dark attuned Soul Harvester, she brings absolute chaos and death to the battlefield with her devastating world shattering strikes. As a prominent member of the notorious half demon Blackheart family, she oversees the freezing southern expanses of the continent known as the Frozen Berg. Serving as both the head executor and chief headhunter for her cursed bloodline, her true goals and intentions during the current rise of the new demon king remain shrouded in complete mystery. Samara cemented her terrifying legacy during the second demon wars at the massacre of Sunwatch Bay, where she singlehandedly slaughtered tens of thousands of humans and entirely shattered the southern advance of the Lightspear forces. Her apocalyptic rampage was only halted when she was challenged and ultimately subjugated by a legendary coalition of heroes consisting of Reinhart Den, Odin Stormrage, and Melisande Sunward. Though she was defeated, she managed to claim the life of Melisande, the elven empress widely believed to be the reincarnate of the ancient goddess Marpha. Samara barely survived the brutal encounter and has remained entirely silent ever since, brooding in the shadows until now.</t>
   </si>
 </sst>
 </file>
@@ -727,11 +799,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4475C369-6A4F-4C74-96DE-3CDD122E599C}">
-  <dimension ref="A3:G42"/>
+  <dimension ref="A3:G54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="136.140625" style="1" customWidth="1"/>
   </cols>
@@ -1380,6 +1452,190 @@
         <v>95</v>
       </c>
     </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="2">
+        <v>25</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="150" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" s="2">
+        <v>50</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B48" t="s">
+        <v>104</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E48" s="2">
+        <v>45</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="150" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B52" t="s">
+        <v>110</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E52" s="2">
+        <v>90</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B53" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E53" s="2">
+        <v>100</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="150" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B54" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E54" s="2">
+        <v>95</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/lores.xlsx
+++ b/lores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daeva\Desktop\Card_game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C5FAD4-F842-4B55-A44B-FAEDB9E5FFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0656AC25-0B0B-44FB-97CD-89A35F399ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E9E6528D-FBE9-4018-A878-CDA73BAA7273}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="130">
   <si>
     <t>name</t>
   </si>
@@ -394,6 +394,36 @@
   </si>
   <si>
     <t>Known universally as the Calamity Demon, Samara Blackheart is an estimated four hundred and ten year old entity whose very existence is treated as a natural disaster. Fighting as a Dark attuned Soul Harvester, she brings absolute chaos and death to the battlefield with her devastating world shattering strikes. As a prominent member of the notorious half demon Blackheart family, she oversees the freezing southern expanses of the continent known as the Frozen Berg. Serving as both the head executor and chief headhunter for her cursed bloodline, her true goals and intentions during the current rise of the new demon king remain shrouded in complete mystery. Samara cemented her terrifying legacy during the second demon wars at the massacre of Sunwatch Bay, where she singlehandedly slaughtered tens of thousands of humans and entirely shattered the southern advance of the Lightspear forces. Her apocalyptic rampage was only halted when she was challenged and ultimately subjugated by a legendary coalition of heroes consisting of Reinhart Den, Odin Stormrage, and Melisande Sunward. Though she was defeated, she managed to claim the life of Melisande, the elven empress widely believed to be the reincarnate of the ancient goddess Marpha. Samara barely survived the brutal encounter and has remained entirely silent ever since, brooding in the shadows until now.</t>
+  </si>
+  <si>
+    <t>Rin Blackheart</t>
+  </si>
+  <si>
+    <t>The Obsidian Ember</t>
+  </si>
+  <si>
+    <t>Alastor Blackheart</t>
+  </si>
+  <si>
+    <t>Master of Darkness</t>
+  </si>
+  <si>
+    <t>Earth, Fire</t>
+  </si>
+  <si>
+    <t>Born at the height of the second demon wars, seventy two year old Rin is the youngest member of the notorious Blackheart family. Despite her dark lineage, she is a remarkably smart and well mannered half demon Warrior who harbors a genuine fondness for humanity. Wielding a massive obsidian blade naturally imbued with fierce Fire magic, she is a formidable melee combatant who actively fights for a peaceful coexistence rather than the destruction her kin are known for. Her goodwill was met with profound tragedy when she was hunted and captured by Serilla, the terrifying hidden weapon of the Moonlight Scripture. Enduring brutal torture and indefinite imprisonment within the citadel dungeons, her hope almost faded entirely until her former partner Morrigan Crow orchestrated her escape following a successful artifact retrieval. Now finally reunited, the two have turned their backs on the treacherous human capital, charting a perilous course deep through the dark glade toward the freezing expanse of the Frozen Berg.</t>
+  </si>
+  <si>
+    <t>Estimated to be five hundred and fifty years old, Alastor is a profoundly mysterious and expressionless Warrior who commands both Earth and Fire in a seamless blend of melee and magical combat. Whispered to be the very first half demon in existence, he made history as the original demonfolk to converse on equal grounds with the higher races in a noble bid for lasting peace. Tragically, these diplomatic efforts were shattered when the elven king fell to an unforeseeable corruption, transforming into the first demon king and immediately slaughtering Alastor's vulnerable kin. Because of his close proximity to the tragic event, many wrongfully blamed Alastor for the corruption, marking him as the primary architect behind the fall of the elven kingdom. Despite the heavy accusations, he fought alongside the ancient goddess Marpha to subjugate the mad king before vanishing entirely into the icy depths of the Frozen Berg. After his remaining kin played a major role in reclaiming the dark glade during the first demon war, this ancient pioneer has stepped out of the shadows once more, reappearing after five centuries of silence to face a world at the brink of total annihilation.</t>
+  </si>
+  <si>
+    <t>At one hundred and forty nine years old, Freya Blackheart is a Dark Berserker whose terrifying true nature earned her the moniker of The Great Cold among her fellow demonfolk. She cleverly infiltrated the ranks of the human citadel templars under a highly skittish guise, aiming to locate the living weapon Serilla and rescue a captive kin hidden deep within the dungeons. Her masterful deception held strong for a time, successfully hiding her dark origins until she was eventually cornered and exposed by the holy cleric Sylas and the ranger Kaelen. Forced to drop her timid facade, Freya revealed her true form as a vicious half demon shapeshifter hailing from the brutal Frozen Berg. Contrary to the quiet and cowardly persona she carefully crafted for the church, her actual personality is incredibly loud, mad, and unapologetically brutish. Driven by a highly cynical worldview and an insatiable bloodlust, she is a monumental threat on the battlefield, gleefully crushing anyone foolish enough to find themselves on the wrong end of her massive troll grade greatsword.</t>
+  </si>
+  <si>
+    <t>Freya Blackheart</t>
+  </si>
+  <si>
+    <t>The Great Cold</t>
   </si>
 </sst>
 </file>
@@ -799,10 +829,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4475C369-6A4F-4C74-96DE-3CDD122E599C}">
-  <dimension ref="A3:G54"/>
+  <dimension ref="A3:G60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="136.140625" style="1" customWidth="1"/>
@@ -1636,6 +1667,98 @@
         <v>119</v>
       </c>
     </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B58" t="s">
+        <v>121</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E58" s="2">
+        <v>75</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+      <c r="A59" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B59" t="s">
+        <v>123</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E59" s="2">
+        <v>85</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B60" t="s">
+        <v>129</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E60" s="2">
+        <v>65</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/lores.xlsx
+++ b/lores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daeva\Desktop\Card_game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0656AC25-0B0B-44FB-97CD-89A35F399ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7ED43EF-CD6E-4405-BAB5-56EB4C5FF719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E9E6528D-FBE9-4018-A878-CDA73BAA7273}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E9E6528D-FBE9-4018-A878-CDA73BAA7273}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -285,9 +285,6 @@
     <t>Lightfoot Thunder</t>
   </si>
   <si>
-    <t>Eamon is a thirty nine year old Air Scout whose sharp wit and easygoing sarcasm make him a memorable, if somewhat unreliable, presence in the local taverns. Earning the nickname Lightfoot Thunder for his swift melee strikes and evasive maneuvers, he deliberately avoids the escalating war against the demon king by exclusively traveling between small villages to accept only the safest, lowest grade quests. This cautious approach ensures his coin purse stays reasonably full while completely eliminating the risk of facing actual danger, a lifestyle that suits his pragmatic mindset perfectly. His comfortable routine was entirely upended following a coincidental reunion with his longtime friend Alden, who guilted the reluctant scout into joining a far more dangerous expedition. While Eamon constantly complains about the sudden increase in peril, he has found a compelling reason to stick around. He has taken a keen interest in Alden’s young niece, secretly desiring a much closer and intimate relationship with her, even if his charming advances are currently falling flat.</t>
-  </si>
-  <si>
     <t>Yvaine Ashcroft</t>
   </si>
   <si>
@@ -424,6 +421,9 @@
   </si>
   <si>
     <t>The Great Cold</t>
+  </si>
+  <si>
+    <t>Eamon is a thirty nine year old Air Scout whose sharp wit and easygoing sarcasm make him a memorable, if somewhat unreliable, presence in the local taverns. Earning the nickname Lightfoot Thunder for his swift melee strikes and evasive maneuvers, he deliberately avoids the escalating war against the demon king by exclusively traveling between small villages to accept only the safest, lowest grade quests. This cautious approach ensures his coin purse stays reasonably full while completely eliminating the risk of facing actual danger, a lifestyle that suits his pragmatic mindset perfectly. His comfortable routine was entirely upended following a coincidental reunion with his longtime friend Alden, who guilted the reluctant scout into joining a far more dangerous expedition. While Eamon constantly complains about the sudden increase in peril, he has found a compelling reason to stick around. He has taken a keen interest in Alden’s young niece, secretly desiring to impress her, even if his charming advances are currently falling flat.</t>
   </si>
 </sst>
 </file>
@@ -1365,15 +1365,15 @@
         <v>8</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>83</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>55</v>
@@ -1388,7 +1388,7 @@
         <v>15</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -1416,10 +1416,10 @@
     </row>
     <row r="40" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" t="s">
         <v>87</v>
-      </c>
-      <c r="B40" t="s">
-        <v>88</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>51</v>
@@ -1434,15 +1434,15 @@
         <v>43</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" t="s">
         <v>90</v>
-      </c>
-      <c r="B41" t="s">
-        <v>91</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>6</v>
@@ -1457,15 +1457,15 @@
         <v>8</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>55</v>
@@ -1480,7 +1480,7 @@
         <v>8</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1508,10 +1508,10 @@
     </row>
     <row r="46" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>51</v>
@@ -1526,18 +1526,18 @@
         <v>8</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="150" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B47" t="s">
+        <v>100</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>33</v>
@@ -1549,21 +1549,21 @@
         <v>8</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E48" s="2">
         <v>45</v>
@@ -1572,7 +1572,7 @@
         <v>43</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -1600,16 +1600,16 @@
     </row>
     <row r="52" spans="1:7" ht="150" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B52" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="E52" s="2">
         <v>90</v>
@@ -1618,21 +1618,21 @@
         <v>8</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B53" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E53" s="2">
         <v>100</v>
@@ -1641,30 +1641,30 @@
         <v>8</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="150" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B54" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>51</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E54" s="2">
         <v>95</v>
       </c>
       <c r="F54" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G54" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -1692,10 +1692,10 @@
     </row>
     <row r="58" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B58" t="s">
         <v>120</v>
-      </c>
-      <c r="B58" t="s">
-        <v>121</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>42</v>
@@ -1704,24 +1704,24 @@
         <v>72</v>
       </c>
       <c r="E58" s="2">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>8</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B59" t="s">
         <v>122</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>72</v>
@@ -1730,18 +1730,18 @@
         <v>85</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B60" t="s">
         <v>128</v>
-      </c>
-      <c r="B60" t="s">
-        <v>129</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>51</v>
@@ -1756,7 +1756,7 @@
         <v>8</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/lores.xlsx
+++ b/lores.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daeva\Desktop\Card_game\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/76651bd78386298a/Desktop/card_game/wayfarers-hearth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7ED43EF-CD6E-4405-BAB5-56EB4C5FF719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{C7ED43EF-CD6E-4405-BAB5-56EB4C5FF719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B81E5577-6924-4633-82A0-C62054447E79}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E9E6528D-FBE9-4018-A878-CDA73BAA7273}"/>
+    <workbookView xWindow="14835" yWindow="165" windowWidth="13395" windowHeight="12300" xr2:uid="{E9E6528D-FBE9-4018-A878-CDA73BAA7273}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -533,9 +533,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -573,7 +573,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -679,7 +679,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -821,7 +821,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1704,7 +1704,7 @@
         <v>72</v>
       </c>
       <c r="E58" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>8</v>
